--- a/Result/checksun_type/原料.xlsx
+++ b/Result/checksun_type/原料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>130.3</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>130.85</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>128.61</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>130.85</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>128.61</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2226.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4665.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4665.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>6404.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>5469.46</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>5469.46</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-288.5135107143324</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2226</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2226.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>130.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>131.2</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>128.41</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>128.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>4059.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>5932.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>5932</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>6584.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>5543.46</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>5543.46</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>13.15029352026431</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>4059</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>4059.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>129.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>131.38</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>128.28</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>131.38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>128.28</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>6801.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>7372.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>7372.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>6841.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>5572.34</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>5572.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>247.236074801106</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>6801</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6801.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>129.2</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>131.45</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>128.13</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>128.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>8198.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>8459.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>8459.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>6903.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>5592.7</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>5592.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>279.028759673698</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>8198</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>8198.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>128.5</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>131.38</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>127.93</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>131.38</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>127.93</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>2045.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>7135.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>7135.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>6268.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>5466.44</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>5466.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>164.8029966461982</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>2045</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2045.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>128.9</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>131.55</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>127.8</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>131.55</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>127.8</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>8557.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>8143.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>8143</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>6419.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>5470.16</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>5470.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>654.9875138695488</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>8557</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>8557.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>128.8</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>131.65</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>127.65</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>131.65</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>127.65</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>11262.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7237.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7237</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5795.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>5341.34</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>5341.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>634.1444129789943</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>11262</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>11262.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>129.0</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>131.82</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>127.53</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>131.82</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>127.53</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>12236.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>6310.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>6310</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>5171.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>5151.14</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>5151.14</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>291.8991112432377</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>12236</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>12236.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>129.4</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>131.9</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>127.4</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>127.4</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1577.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>5346.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>5346.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4385.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>4949.88</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>4949.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-311.8048594951015</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1577</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1577.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>129.8</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>131.82</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>127.22</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>131.82</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>127.22</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>7083.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>5402.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>5402</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4748.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>5097.72</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>5097.72</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-21.06750128218846</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>7083</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>7083.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>130.1</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>131.7</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>127.02</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>127.02</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4027.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4695.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4695</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>4863.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>5151.8</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>5151.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-194.9045787893774</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4027</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4027.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>74.24000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>74.49</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>75.24</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>75.23999999999999</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>308.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>551.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>551.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>863.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1290.88</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1290.88</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-131.622686315784</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>308</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>308.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>73.9</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>74.43</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>75.26</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>75.26000000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>150.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1114.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1114.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1031.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1331.94</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1331.94</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-101.2782191199866</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>150</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>73.94</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>74.34</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>75.31</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>75.31</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>697.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1193.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1193.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1078.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1371.9</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1371.9</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-37.38332958599062</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>697</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>697.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>74.52000000000001</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>74.34</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>75.39</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>75.39</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>946.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1199.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1199.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1252.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1371.2</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1371.2</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-3.37693990935395</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>946</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>946.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>75.02000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>74.29</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>75.42</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>75.42</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>658.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1133.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1133.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1238.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1373.1</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1373.1</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>18.64565033974668</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>658</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>658.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>75.78</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>74.29</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>75.46</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>75.45999999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>3120.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1175.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1175.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1201.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1414.94</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1414.94</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>80.29772032632854</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>3120</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>3120.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>76.8</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>74.34</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>75.52</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>75.52</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>548.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>949.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>949.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1005.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1370.62</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1370.62</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-98.28138399020929</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>548</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>548.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>76.96000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>74.28</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>75.52</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>75.52</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>724.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>963.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>963.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1017.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1387.96</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1387.96</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-74.31291215704164</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>724</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>724.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>76.70000000000002</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>74.09</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>75.51</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>74.09</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>75.51000000000001</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>618.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1305.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1305.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1003.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1397.72</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1397.72</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-56.27534838976499</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>618</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>618.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>75.84</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>73.95</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>75.46</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>75.45999999999999</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>866.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1342.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1342.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1066.1</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1425.92</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1425.92</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-17.14042342259222</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>866</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>866.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>74.86</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>73.74</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>75.43</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>75.43000000000001</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1992.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1227.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1227.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1038.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1421.24</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1421.24</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>12.80734165274703</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1992</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1992.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>27.0</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>27.32</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>28.96</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>6377966.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>6176987.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>6176987.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>5819335.3</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>7057711.28</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>7057711.28</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>318810.7876168946</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>6377966</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>6377966.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>26.65</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>27.34</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>29</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>14065095.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>5502534.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>5502534.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>5577139.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>7141675.4</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>7141675.4</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>354777.3309102692</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>14065095</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>14065095.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>26.32</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>27.38</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>29.06</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>2914289.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>3848013.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>3848013.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>4769960.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>7033263.38</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>7033263.38</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-430133.4762031334</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2914289</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2914289.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>26.41</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>27.52</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>29.16</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>4874674.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>4326733.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>4326733.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>5162658.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>7253837.46</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>7253837.46</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-341343.5050721681</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>4874674</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>4874674.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>26.76</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>29.27</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>29.27</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>2652914.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>4882698.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>4882698.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>5090432.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>7327974.3</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>7327974.3</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-412351.0997039247</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>2652914</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>2652914.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>26.91</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>27.88</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>29.36</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>29.36</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>3005699.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>5461683.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>5461683</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>5213400.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>7669422.94</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>7669422.94</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-261017.9813312953</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>3005699</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>3005699.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>27.11</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>28.05</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>29.48</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>29.48</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>5792491.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>5651744.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>5651744.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>5390737.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>7832741.84</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>7832741.84</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-73304.13432285003</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>5792491</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>5792491.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>29.6</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>5307889.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>5691908.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>5691908</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>5278991.6</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>8214914.5</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>8214914.5</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-101108.3480849694</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>5307889</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>5307889.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>27.29</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>29.72</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>29.72</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>7654500.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>5998583.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>5998583.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>4953026.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>8631788.52</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>8631788.52</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-85295.99817067571</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>7654500</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>7654500.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>27.27</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>29.8</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>5547836.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>5298166.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>5298166.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>4494096.0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>8670075.9</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>8670075.9</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-311083.2483584471</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>5547836</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>5547836.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>27.34</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>28.52</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>29.89</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>29.89</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>3956007.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>4965118.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>4965118.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>4940124.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>8893843.2</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>8893843.199999999</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-396812.3468996035</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>3956007</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>3956007.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>14.67</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>16.85</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>1877.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>1612.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>1612.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1484.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2404.96</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2404.96</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-218.5414979881389</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>1877</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>1877.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>14.69</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>15.54</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>16.91</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1133.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1407.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1407.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>1535.1</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2509.52</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2509.52</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-260.0078192599899</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1133</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1133.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>14.77</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>15.65</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>17</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>2840.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1448.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1448.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1659.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2535.26</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2535.26</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-230.2451418176345</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>2840</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>2840.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>14.88</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>15.79</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>17.09</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>1469.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1343.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1343.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>2211.1</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2531.16</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2531.16</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-362.3968475493537</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>1469</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>1469.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>15.05</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>15.94</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>17.18</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>17.18</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>742.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1287.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1287.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>2279.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>2582.94</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>2582.94</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-391.3493968964758</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>742</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>742.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>15.14</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>16.06</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>17.26</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>17.26</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>852.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1357.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1357.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>2336.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>2620.3</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>2620.3</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-340.8405603603476</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>852</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>852.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>15.33</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>16.18</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>17.34</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>17.34</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>1339.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1663.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1663</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>2457.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>2719.2</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>2719.2</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-268.297916724438</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>1339</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>1339.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>15.42</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>17.43</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>17.43</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>2315.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1870.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1870.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>2981.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2774.36</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2774.36</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-207.2620716472657</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>2315</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>2315.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>15.44</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>16.44</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>17.52</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>17.52</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1190.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3078.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3078.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>2915.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2807.38</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2807.38</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-217.2372189781881</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1190</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1190.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>15.56</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>16.57</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>17.59</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>17.59</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1092.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>3271.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>3271.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>2994.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2855.18</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2855.18</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-103.1932430588572</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1092</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1092.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>15.68</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>16.69</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>17.67</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>17.67</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>2379.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>3316.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>3316</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>3207.2</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>2889.22</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>2889.22</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>73.91219550657479</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>2379</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>2379.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>38.02</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>38.75</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>39.85</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>39.85</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>160.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>332.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>332.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>417.4</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>416.82</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>416.82</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-18.94398584934049</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>160</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>38.21</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>38.83</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>39.9</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>39.9</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>616.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>527.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>527.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>435.3</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>426.08</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>426.08</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>4.336333525618045</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>616</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>616.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>38.16</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>38.91</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>39.97</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>39.97</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>131.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>606.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>606.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>410.9</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>424.46</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>424.46</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-11.41807927892756</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>131</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>38.26000000000001</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>38.99</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>40.03</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>40.03</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>381.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>604.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>604.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>458.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>473.7</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>473.7</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>18.44769097454042</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>381</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>381.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>38.53</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>39.11</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>40.12</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>40.12</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>374.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>537.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>537</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>448.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>469.66</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>469.66</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>33.66851665897542</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>374</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>374.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>38.73999999999999</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>39.22</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>40.2</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>39.22</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>40.2</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1136.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>502.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>502.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>425.1</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>467.1</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>467.1</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>54.96010632749056</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1136</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1136.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>38.63</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>39.24</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>40.24</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>40.24</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1010.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>343.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>343</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>395.3</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>456.16</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>456.16</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>1.770944913673247</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1010</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1010.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>38.82</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>39.34</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>40.32</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>40.32</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>122.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>215.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>215.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>346.5</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>443.58</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>443.58</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-60.7768194244112</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>122</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>38.95999999999999</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>39.43</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>40.38</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>40.38</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>43.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>312.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>312.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>354.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>454.54</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>454.54</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-52.81731064223146</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>43</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>39.04</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>40.44</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>40.44</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>201.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>359.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>359.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>446.4</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>471.58</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>471.58</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-31.09596557332361</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>201</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>201.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>39.01</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>40.49</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>40.49</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>339.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>347.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>347.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>468.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>476.42</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>476.42</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-15.88347384726507</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>339</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>339.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>47.93</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>48.35</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>49.48</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>49.48</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>1095.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>991.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>991.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1153.2</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1779.48</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1779.48</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-152.7184353807731</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1095</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1095.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>47.96</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>48.42</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>49.54</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>49.54</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>797.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1188.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1188.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1059.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1804.04</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1804.04</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-172.2550328369114</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>797</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>797.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>47.96</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>49.61</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>49.61</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>604.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1271.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1271.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1094.2</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1823.5</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1823.5</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-162.0839208872189</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>604</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>604.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>47.95</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>48.54</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>49.69</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>49.69</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>1402.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1364.8</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1364.8</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1178.1</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1861.44</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1861.44</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-121.0864780702577</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>1402</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>1402.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>48.05</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>48.59</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>49.78</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>49.78</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1060.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1148.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1148.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1323.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1895.4</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1895.4</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-143.6941855435182</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1060</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1060.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>48.19</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>48.64</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>49.88</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>49.88</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>2079.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1314.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1314.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1280.7</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1930.3</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1930.3</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-134.216118164479</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2079</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2079.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>48.34</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>48.59</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>49.97</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>49.97</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>1211.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>931.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>931</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1307.0</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1923.32</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1923.32</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-225.0611605456916</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>1211</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>1211.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>48.48</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>48.61</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>50.09</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>50.09</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>1072.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>917.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>917.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1359.2</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>1977.1</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>1977.1</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-253.8018939279348</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>1072</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>1072.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>48.62</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>48.63</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>50.23</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>48.63</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>50.23</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>320.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>991.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>991.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1436.1</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2068.06</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2068.06</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-270.9028739765704</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>320</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>48.72</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>50.34</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>50.34</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1892.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1497.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1497.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1564.6</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2185.7</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2185.7</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-205.0863142611722</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1892</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1892.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>48.58</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>48.66</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>50.43</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>48.66</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>50.43</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>160.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1246.6</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1246.6</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>1574.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2223.0</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2223</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-272.1667177298473</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>160</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>14.08</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>14.73</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>14.73</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>1410555.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>1409250.6</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>1409250.6</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>1528160.2</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>2400521.24</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>2400521.24</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-171176.3716088689</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>1410555</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>1410555.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>14.05</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>14.77</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>14.77</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>1601795.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>1292239.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>1292239.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>1672455.5</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>2574731.26</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>2574731.26</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-174660.554899578</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>1601795</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>1601795.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>14.03</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>14.83</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>14.83</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>1434878.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>1466283.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>1466283.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>2144686.5</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>2753950.9</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>2753950.9</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-193890.0826398917</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>1434878</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>1434878.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>14.12</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>14.14</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>14.9</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>14.9</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1447775.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1470800.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>1470800.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>2117736.6</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>3130612.66</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>3130612.66</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-196552.2264603437</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1447775</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1447775.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>14.2</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>14.95</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>14.95</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>1151250.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>1414037.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>1414037.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>2061521.4</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>3299007.36</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>3299007.36</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-194717.3881159772</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>1151250</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>1151250.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>14.2</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>14.19</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>14.99</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>825499.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>1647069.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>1647069.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>2202858.1</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>3941202.8</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>3941202.8</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-153371.4623341688</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>825499</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>825499.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>14.27</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>14.21</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>2472016.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>2052671.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>2052671.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>2333964.3</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>4694577.76</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>4694577.76</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-53926.40899107931</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>2472016</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>2472016.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>14.37</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>14.22</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>15.09</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>15.09</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>1457461.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>2823089.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>2823089.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>2310857.9</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>5175245.04</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>5175245.04</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-86348.63960841252</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>1457461</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>1457461.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>14.25</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>14.23</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>15.08</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>15.08</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>1163961.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>2764673.0</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>2764673</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>2344065.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>5197831.52</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>5197831.52</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-20879.91050430248</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>1163961</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>1163961.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>14.21</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>14.26</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>15.08</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>15.08</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>2316412.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>2709005.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>2709005.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>2443206.4</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>5242964.26</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>5242964.26</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>104838.9850195795</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>2316412</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>2316412.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>14.18</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>14.27</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>15.08</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>15.08</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>2853508.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>2758646.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>2758646.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>2636464.2</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>5260233.4</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>5260233.4</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>157216.2648744262</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>2853508</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>2853508.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>61.74</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>1408.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>1390.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>1390</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>1874.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>2505.32</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>2505.32</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-162.3915940610709</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>1408</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>1408.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>61.74</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>897.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>1319.8</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>1319.8</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>2147.2</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>2523.66</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>2523.66</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-161.590655999162</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>897</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>897.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>61.56</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>61.77</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>61.77</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>62.14</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>2127.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>1720.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>1720</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>2206.6</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>2581.7</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>2581.7</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-99.92536391075078</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>2127</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>2127.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>61.72000000000001</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>61.82</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>62.15</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>62.15</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>1337.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>1696.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>1696</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>2141.2</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>2592.12</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>2592.12</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-140.0490407876364</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>1337</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1337.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>61.88</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>61.86</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>62.18</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>62.18</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>1181.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>1820.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>1820</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>2048.4</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>2632.5</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>2632.5</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-107.7239705836289</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1181</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1181.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>61.96</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>61.91</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>62.19</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>62.19</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>1057.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>2359.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>2359.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>2006.4</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>2638.44</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>2638.44</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-40.98372848563167</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>1057</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>1057.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>61.98</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>61.94</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>2898.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>2974.6</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>2974.6</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>2218.7</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>2658.94</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>2658.94</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>69.10889338599463</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>2898</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>2898.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>61.96</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>61.98</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>61.98</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>62.21</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>2007.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>2693.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>2693.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>2055.5</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>2633.78</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>2633.78</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>26.66589272453211</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>2007</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>2007.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>61.8</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>61.99</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>1957.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>2586.4</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>2586.4</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>1968.1</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2647.68</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2647.68</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>60.54496703942414</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>1957</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>1957.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>61.7</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>62.03</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>62.2</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>62.03</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>62.2</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>3877.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>2276.8</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>2276.8</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>1891.3</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2631.9</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2631.9</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>112.1384672378617</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>3877</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>3877.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>61.6</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>62.08</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>62.21</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>4134.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1653.6</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1653.6</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>1674.6</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2583.16</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2583.16</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-23.8757634514368</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>4134</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>4134.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>46.14</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>52.06</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>52.06</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>594.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>607.8</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>607.8</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>628.1</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>1629.78</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>1629.78</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-166.1313006000929</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>594</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>594.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>46.22</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>48.08</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>52.35</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>52.35</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>326.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>562.8</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>562.8</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>640.3</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>1690.9</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>1690.9</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-174.6854545135704</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>326</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>326.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>46.36</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>48.23</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>52.69</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>48.23</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>52.69</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>1625.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>807.4</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>807.4</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>772.9</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>1792.48</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>1792.48</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-151.9526224430539</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>1625</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>1625.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>46.82000000000001</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>48.43</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>53.07</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>53.07</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>382.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>534.0</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>534</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>754.2</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>1989.68</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>1989.68</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-253.2288401122069</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>382</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>382.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>47.22</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>53.39</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>53.39</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>112.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>486.8</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>486.8</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>897.3</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>2106.8</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>2106.8</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-255.6866924927036</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>112</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>47.6</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>53.63</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>53.63</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>369.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>648.4</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>648.4</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>1069.6</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>2269.8</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>2269.8</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-221.137671161531</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>369</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>369.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>48.0</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>49.06</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>53.92</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>53.92</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>1549.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>717.8</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>717.8</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>1129.9</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>2470.54</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>2470.54</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-191.4198667183725</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>1549</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>1549.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>48.48</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>49.24</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>54.29</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>54.29</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>258.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>738.4</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>738.4</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>1170.5</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>2640.88</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>2640.88</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-268.5580079882045</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>258</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>258.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>49.0</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>49.36</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>54.62</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>54.62</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>146.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>974.4</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>974.4</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>1545.3</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>2949.64</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>2949.64</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-230.8425666598139</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>146</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>49.33</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>49.51</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>54.95</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>54.95</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>920.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>1307.8</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>1307.8</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>1569.6</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>3235.82</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>3235.82</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-156.7189873814054</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>920</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>920.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>49.64</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>49.62</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>55.21</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>55.21</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>716.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>1490.8</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>1490.8</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>1699.1</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>3642.78</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>3642.78</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-128.1596245772002</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>716</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>716.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
